--- a/src/data/OpenCartTestData.xlsx
+++ b/src/data/OpenCartTestData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srava\OneDrive\Desktop\Tecnics\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srava\OneDrive\Desktop\TechTip24\Documents\OpencartWebFramework_PW\src\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2488B430-6DF1-4440-AA56-7A70D54EBDE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A841C754-50C9-4DCB-8773-30C4FD43EAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{21AB45DD-5925-4239-9BA2-0F814CCABE8A}"/>
   </bookViews>
@@ -42,9 +42,6 @@
     <t>password</t>
   </si>
   <si>
-    <t>abcc@gmail.com</t>
-  </si>
-  <si>
     <t>pwd@123</t>
   </si>
   <si>
@@ -54,10 +51,13 @@
     <t>pw123</t>
   </si>
   <si>
-    <t>pwbatchtest@open.com</t>
-  </si>
-  <si>
     <t xml:space="preserve">   </t>
+  </si>
+  <si>
+    <t>abccd@gmail.com</t>
+  </si>
+  <si>
+    <t>pwbatchtest1@open.com</t>
   </si>
 </sst>
 </file>
@@ -436,26 +436,26 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
